--- a/Raw_Data/v7a_2040_bio_critical_load.xlsx
+++ b/Raw_Data/v7a_2040_bio_critical_load.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1AF3808B-2E1C-4020-B52A-70BA17D10A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A40D84D-B0B6-435C-9A6E-168452E2BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-2730" windowWidth="19410" windowHeight="20985" firstSheet="8" activeTab="11" xr2:uid="{5BDD99AF-CED3-49E3-9A38-20A09C5DF3D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="11" xr2:uid="{5BDD99AF-CED3-49E3-9A38-20A09C5DF3D4}"/>
   </bookViews>
   <sheets>
     <sheet name="bio_critical_load (11)" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,8 @@
     <sheet name="bio_critical_load (3)" sheetId="10" r:id="rId9"/>
     <sheet name="bio_critical_load (2)" sheetId="9" r:id="rId10"/>
     <sheet name="bio_critical_load (1)" sheetId="11" r:id="rId11"/>
-    <sheet name="bio_critical_load" sheetId="8" r:id="rId12"/>
+    <sheet name="bio_critical_load (12)" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -240,9 +241,6 @@
     <t>Scenario: OPT Health -50 AAE -50 v7a</t>
   </si>
   <si>
-    <t>Scenario: LRTAP_Baseline_v7</t>
-  </si>
-  <si>
     <t>Scenario: OPT Health -50 AAE -35 v7a</t>
   </si>
   <si>
@@ -253,6 +251,9 @@
   </si>
   <si>
     <t>Scenario: OPT Health -50 AAE -45 v7a</t>
+  </si>
+  <si>
+    <t>Scenario: Baseline_v7a</t>
   </si>
 </sst>
 </file>
@@ -3084,7 +3085,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -5045,7 +5046,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -6995,7 +6996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FE8E4A-40EB-4F78-9A25-51FEB8556E01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BFB4A0-4779-433E-AB3F-B147B5D1B459}">
   <dimension ref="A2:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -7006,7 +7007,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -7090,7 +7091,7 @@
         <v>36.299999999999997</v>
       </c>
       <c r="H10">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7166,19 +7167,19 @@
         <v>54.3</v>
       </c>
       <c r="D12">
-        <v>78.2</v>
+        <v>78.5</v>
       </c>
       <c r="E12">
-        <v>195.8</v>
+        <v>196.4</v>
       </c>
       <c r="F12">
         <v>37.200000000000003</v>
       </c>
       <c r="G12">
-        <v>68.2</v>
+        <v>68.7</v>
       </c>
       <c r="H12">
-        <v>101.6</v>
+        <v>102.2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -7196,7 +7197,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>400.7</v>
+        <v>401.3</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -7213,7 +7214,7 @@
         <v>77</v>
       </c>
       <c r="E13">
-        <v>276.39999999999998</v>
+        <v>276.5</v>
       </c>
       <c r="F13">
         <v>19.8</v>
@@ -7222,7 +7223,7 @@
         <v>57.7</v>
       </c>
       <c r="H13">
-        <v>140.5</v>
+        <v>140.6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -7240,7 +7241,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>437.7</v>
+        <v>437.8</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -7257,7 +7258,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>391.8</v>
+        <v>391.9</v>
       </c>
       <c r="F14">
         <v>0.7</v>
@@ -7266,7 +7267,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>426</v>
+        <v>426.1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -7284,7 +7285,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>370</v>
+        <v>370.1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -7354,7 +7355,7 @@
         <v>98.6</v>
       </c>
       <c r="H16">
-        <v>425.7</v>
+        <v>425.8</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -7372,7 +7373,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>579.1</v>
+        <v>579.20000000000005</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -7386,16 +7387,16 @@
         <v>30.6</v>
       </c>
       <c r="D17">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="E17">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="F17">
         <v>21.6</v>
       </c>
       <c r="G17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H17">
         <v>1.2</v>
@@ -7416,7 +7417,7 @@
         <v>99.8</v>
       </c>
       <c r="N17">
-        <v>108.2</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -7565,7 +7566,7 @@
         <v>99.9</v>
       </c>
       <c r="E21">
-        <v>345.1</v>
+        <v>345.3</v>
       </c>
       <c r="F21">
         <v>24.5</v>
@@ -7574,7 +7575,7 @@
         <v>99.8</v>
       </c>
       <c r="H21">
-        <v>341.2</v>
+        <v>341.6</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -7592,7 +7593,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>346.8</v>
+        <v>347.1</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -7609,7 +7610,7 @@
         <v>70.400000000000006</v>
       </c>
       <c r="E22">
-        <v>341.3</v>
+        <v>341.6</v>
       </c>
       <c r="F22">
         <v>17.3</v>
@@ -7618,7 +7619,7 @@
         <v>48.7</v>
       </c>
       <c r="H22">
-        <v>175.5</v>
+        <v>175.6</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -7636,7 +7637,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>568.70000000000005</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -7653,7 +7654,7 @@
         <v>41.5</v>
       </c>
       <c r="E23">
-        <v>99.3</v>
+        <v>99.4</v>
       </c>
       <c r="F23">
         <v>6.7</v>
@@ -7715,7 +7716,7 @@
         <v>70.400000000000006</v>
       </c>
       <c r="K24">
-        <v>507.9</v>
+        <v>508</v>
       </c>
       <c r="L24">
         <v>34.200000000000003</v>
@@ -7741,7 +7742,7 @@
         <v>58.9</v>
       </c>
       <c r="E25">
-        <v>98.3</v>
+        <v>98.1</v>
       </c>
       <c r="F25">
         <v>27.1</v>
@@ -7750,7 +7751,7 @@
         <v>33</v>
       </c>
       <c r="H25">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -7768,7 +7769,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>217.5</v>
+        <v>217.3</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -7785,7 +7786,7 @@
         <v>91.7</v>
       </c>
       <c r="E26">
-        <v>236.8</v>
+        <v>236.1</v>
       </c>
       <c r="F26">
         <v>18.7</v>
@@ -7794,7 +7795,7 @@
         <v>88.3</v>
       </c>
       <c r="H26">
-        <v>187.4</v>
+        <v>186.5</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -7812,7 +7813,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>358.3</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -7882,7 +7883,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>383.1</v>
+        <v>383.2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -7917,7 +7918,7 @@
         <v>66.2</v>
       </c>
       <c r="E29">
-        <v>407</v>
+        <v>407.1</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -8046,19 +8047,19 @@
         <v>109.3</v>
       </c>
       <c r="D32">
-        <v>89.4</v>
+        <v>89.5</v>
       </c>
       <c r="E32">
-        <v>279.5</v>
+        <v>280.39999999999998</v>
       </c>
       <c r="F32">
         <v>71.599999999999994</v>
       </c>
       <c r="G32">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="H32">
-        <v>187.6</v>
+        <v>188.5</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -8076,7 +8077,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>453.6</v>
+        <v>454.5</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -8093,7 +8094,7 @@
         <v>82.4</v>
       </c>
       <c r="E33">
-        <v>197.4</v>
+        <v>197.6</v>
       </c>
       <c r="F33">
         <v>20.7</v>
@@ -8102,7 +8103,7 @@
         <v>77.099999999999994</v>
       </c>
       <c r="H33">
-        <v>152.5</v>
+        <v>152.80000000000001</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -8120,7 +8121,7 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>348.1</v>
+        <v>348.4</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -8164,7 +8165,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>504.1</v>
+        <v>504.2</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -8263,10 +8264,10 @@
         <v>1445.6</v>
       </c>
       <c r="D37">
-        <v>65.400000000000006</v>
+        <v>65.5</v>
       </c>
       <c r="E37">
-        <v>211.7</v>
+        <v>211.8</v>
       </c>
       <c r="F37">
         <v>927.8</v>
@@ -8284,7 +8285,7 @@
         <v>11</v>
       </c>
       <c r="K37">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="L37">
         <v>509.5</v>
@@ -8293,7 +8294,7 @@
         <v>79.099999999999994</v>
       </c>
       <c r="N37">
-        <v>273.39999999999998</v>
+        <v>273.5</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -8310,7 +8311,7 @@
         <v>94</v>
       </c>
       <c r="E38">
-        <v>383.3</v>
+        <v>383.4</v>
       </c>
       <c r="F38">
         <v>7.4</v>
@@ -8319,7 +8320,7 @@
         <v>83.9</v>
       </c>
       <c r="H38">
-        <v>199.7</v>
+        <v>199.8</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -8337,7 +8338,7 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>492.1</v>
+        <v>492.2</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -8354,7 +8355,7 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>472.4</v>
+        <v>464.3</v>
       </c>
       <c r="F39">
         <v>59.6</v>
@@ -8363,7 +8364,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>462.6</v>
+        <v>454.3</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -8381,7 +8382,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>557</v>
+        <v>550.5</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -8398,7 +8399,7 @@
         <v>69.400000000000006</v>
       </c>
       <c r="E40">
-        <v>196.7</v>
+        <v>196.8</v>
       </c>
       <c r="F40">
         <v>22.6</v>
@@ -8407,7 +8408,7 @@
         <v>49.9</v>
       </c>
       <c r="H40">
-        <v>128.9</v>
+        <v>129</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -8425,7 +8426,7 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>303</v>
+        <v>303.2</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -8442,7 +8443,7 @@
         <v>77.7</v>
       </c>
       <c r="E41">
-        <v>185.7</v>
+        <v>185.9</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -8451,7 +8452,7 @@
         <v>73.7</v>
       </c>
       <c r="H41">
-        <v>147</v>
+        <v>147.19999999999999</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -8469,7 +8470,7 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>397.2</v>
+        <v>397.3</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -8486,7 +8487,7 @@
         <v>72.8</v>
       </c>
       <c r="E42">
-        <v>165</v>
+        <v>165.2</v>
       </c>
       <c r="F42">
         <v>8.3000000000000007</v>
@@ -8495,7 +8496,7 @@
         <v>44.8</v>
       </c>
       <c r="H42">
-        <v>39.799999999999997</v>
+        <v>39.9</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -8513,7 +8514,7 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>286.7</v>
+        <v>286.89999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -8530,7 +8531,7 @@
         <v>99.8</v>
       </c>
       <c r="E43">
-        <v>376.3</v>
+        <v>387.3</v>
       </c>
       <c r="F43">
         <v>1.8</v>
@@ -8539,7 +8540,7 @@
         <v>99.6</v>
       </c>
       <c r="H43">
-        <v>242.1</v>
+        <v>255</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -8557,7 +8558,7 @@
         <v>100</v>
       </c>
       <c r="N43">
-        <v>502.3</v>
+        <v>511.5</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -8574,13 +8575,13 @@
         <v>55.3</v>
       </c>
       <c r="E44">
-        <v>122.9</v>
+        <v>123</v>
       </c>
       <c r="F44">
         <v>6.1</v>
       </c>
       <c r="G44">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="H44">
         <v>35.5</v>
@@ -8601,7 +8602,7 @@
         <v>100</v>
       </c>
       <c r="N44">
-        <v>302.39999999999998</v>
+        <v>302.5</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -8615,7 +8616,7 @@
         <v>303.39999999999998</v>
       </c>
       <c r="D45">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="E45">
         <v>5.3</v>
@@ -8624,7 +8625,7 @@
         <v>124.6</v>
       </c>
       <c r="G45">
-        <v>9.9</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="H45">
         <v>9.5</v>
@@ -8659,19 +8660,19 @@
         <v>643.1</v>
       </c>
       <c r="D46">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="E46">
-        <v>92.5</v>
+        <v>94.9</v>
       </c>
       <c r="F46">
         <v>518.70000000000005</v>
       </c>
       <c r="G46">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="H46">
-        <v>94.7</v>
+        <v>97.4</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -8686,10 +8687,10 @@
         <v>124.4</v>
       </c>
       <c r="M46">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="N46">
-        <v>83.5</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -8706,7 +8707,7 @@
         <v>90</v>
       </c>
       <c r="E47">
-        <v>431.3</v>
+        <v>431.6</v>
       </c>
       <c r="F47">
         <v>19.8</v>
@@ -8715,7 +8716,7 @@
         <v>83.3</v>
       </c>
       <c r="H47">
-        <v>259.89999999999998</v>
+        <v>260.10000000000002</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -8733,7 +8734,7 @@
         <v>100</v>
       </c>
       <c r="N47">
-        <v>687.2</v>
+        <v>687.5</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -8791,19 +8792,19 @@
         <v>97.8</v>
       </c>
       <c r="D49">
-        <v>99.9</v>
+        <v>100</v>
       </c>
       <c r="E49">
-        <v>452.3</v>
+        <v>457.2</v>
       </c>
       <c r="F49">
         <v>74.5</v>
       </c>
       <c r="G49">
-        <v>99.9</v>
+        <v>100</v>
       </c>
       <c r="H49">
-        <v>437.2</v>
+        <v>442.2</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -8821,7 +8822,7 @@
         <v>100</v>
       </c>
       <c r="N49">
-        <v>500.6</v>
+        <v>505.3</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -8876,19 +8877,19 @@
         <v>1330.7</v>
       </c>
       <c r="D51">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="E51">
-        <v>134.1</v>
+        <v>135.30000000000001</v>
       </c>
       <c r="F51">
         <v>877.1</v>
       </c>
       <c r="G51">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="H51">
-        <v>143.9</v>
+        <v>145.4</v>
       </c>
       <c r="I51">
         <v>24.4</v>
@@ -8903,10 +8904,10 @@
         <v>429.1</v>
       </c>
       <c r="M51">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="N51">
-        <v>121.1</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -8917,19 +8918,19 @@
         <v>2776.2</v>
       </c>
       <c r="D52">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="E52">
-        <v>174.5</v>
+        <v>175.2</v>
       </c>
       <c r="F52">
         <v>1804.9</v>
       </c>
       <c r="G52">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="H52">
-        <v>162.19999999999999</v>
+        <v>162.9</v>
       </c>
       <c r="I52">
         <v>32.700000000000003</v>
@@ -8947,10 +8948,19 @@
         <v>59.6</v>
       </c>
       <c r="N52">
-        <v>203.8</v>
+        <v>204.1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C48ADF-B680-4A57-B61E-F082767A2C3B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20733,7 +20743,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -22694,7 +22704,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
